--- a/output/petroleum_production_flat_table.xlsx
+++ b/output/petroleum_production_flat_table.xlsx
@@ -26890,4 +26890,285 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CCB40CA4B69967448E5E142573FA85FC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f19dfd05c72a4aa217b148f0f00ef59">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e9ead7b-6342-4494-9745-aa11ca9090cb" xmlns:ns3="9e595a92-2a84-46d4-9885-e168ac7f98a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d61ddcb55407106f5563e5e5e5e7a99" ns2:_="" ns3:_="">
+    <xsd:import namespace="7e9ead7b-6342-4494-9745-aa11ca9090cb"/>
+    <xsd:import namespace="9e595a92-2a84-46d4-9885-e168ac7f98a1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e9ead7b-6342-4494-9745-aa11ca9090cb" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4b3741f9-8584-47b2-968f-3f53d9bbee55" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9e595a92-2a84-46d4-9885-e168ac7f98a1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0d5f833c-ae06-418d-979f-18c784237a1f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9e595a92-2a84-46d4-9885-e168ac7f98a1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e9ead7b-6342-4494-9745-aa11ca9090cb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9e595a92-2a84-46d4-9885-e168ac7f98a1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C8592C-16EC-49A0-AB24-6EC7DEF3CB4E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB34A29B-688A-43EE-B6D2-008E0DD05143}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0875A02-CFA8-4075-AC1A-48FE83FD1D13}"/>
 </file>
--- a/output/petroleum_production_flat_table.xlsx
+++ b/output/petroleum_production_flat_table.xlsx
@@ -26890,285 +26890,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CCB40CA4B69967448E5E142573FA85FC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f19dfd05c72a4aa217b148f0f00ef59">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e9ead7b-6342-4494-9745-aa11ca9090cb" xmlns:ns3="9e595a92-2a84-46d4-9885-e168ac7f98a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d61ddcb55407106f5563e5e5e5e7a99" ns2:_="" ns3:_="">
-    <xsd:import namespace="7e9ead7b-6342-4494-9745-aa11ca9090cb"/>
-    <xsd:import namespace="9e595a92-2a84-46d4-9885-e168ac7f98a1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7e9ead7b-6342-4494-9745-aa11ca9090cb" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4b3741f9-8584-47b2-968f-3f53d9bbee55" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="23" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9e595a92-2a84-46d4-9885-e168ac7f98a1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0d5f833c-ae06-418d-979f-18c784237a1f}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9e595a92-2a84-46d4-9885-e168ac7f98a1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e9ead7b-6342-4494-9745-aa11ca9090cb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9e595a92-2a84-46d4-9885-e168ac7f98a1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73C8592C-16EC-49A0-AB24-6EC7DEF3CB4E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB34A29B-688A-43EE-B6D2-008E0DD05143}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0875A02-CFA8-4075-AC1A-48FE83FD1D13}"/>
 </file>
--- a/output/petroleum_production_flat_table.xlsx
+++ b/output/petroleum_production_flat_table.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V279"/>
+  <dimension ref="A1:V312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25016,6 +25016,2910 @@
         </is>
       </c>
       <c r="V279" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>ในทะเล_10A 11A_10A/11A</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>9</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>10A 11A</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>10A/11A</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I280" t="n">
+        <v>412.52</v>
+      </c>
+      <c r="J280" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="K280" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="L280" t="n">
+        <v>274.36</v>
+      </c>
+      <c r="M280" t="n">
+        <v>710.65</v>
+      </c>
+      <c r="N280" t="n">
+        <v>30</v>
+      </c>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Chevron Thailand / 10A &amp; 11A</t>
+        </is>
+      </c>
+      <c r="S280" t="n">
+        <v>14</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Songkhla Basin</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ในทะเล_B12/27_ไพลิน / มรกต</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>9</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>B12/27</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ไพลิน / มรกต</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>116.24</v>
+      </c>
+      <c r="I281" t="n">
+        <v>20271.88</v>
+      </c>
+      <c r="J281" t="n">
+        <v>4586.7</v>
+      </c>
+      <c r="K281" t="n">
+        <v>4172.06</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
+        <v>24443.94</v>
+      </c>
+      <c r="N281" t="n">
+        <v>30</v>
+      </c>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>Chevron Thailand / Pailin &amp; Morakot</t>
+        </is>
+      </c>
+      <c r="S281" t="n">
+        <v>15</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>ในทะเล_B12/27_ไพลินเหนือ</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>9</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>B12/27</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>ไพลินเหนือ</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>176.15</v>
+      </c>
+      <c r="I282" t="n">
+        <v>30721.19</v>
+      </c>
+      <c r="J282" t="n">
+        <v>5983.86</v>
+      </c>
+      <c r="K282" t="n">
+        <v>5442.92</v>
+      </c>
+      <c r="L282" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" t="n">
+        <v>36164.11</v>
+      </c>
+      <c r="N282" t="n">
+        <v>30</v>
+      </c>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>Chevron Thailand / North Pailin</t>
+        </is>
+      </c>
+      <c r="S282" t="n">
+        <v>16</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Chevron Thailand</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>ในทะเล_B8/32 G4/43 G4/48_เบญจมาศ</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>9</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>B8/32 G4/43 G4/48</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>เบญจมาศ</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>73.63</v>
+      </c>
+      <c r="I283" t="n">
+        <v>12840.46</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" t="n">
+        <v>18035.73</v>
+      </c>
+      <c r="M283" t="n">
+        <v>30876.19</v>
+      </c>
+      <c r="N283" t="n">
+        <v>30</v>
+      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>Chevron Offshore / Benchamas</t>
+        </is>
+      </c>
+      <c r="S283" t="n">
+        <v>17</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Chevron Offshore</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>ในทะเล_B8/32 G4/43 G4/48_ชบา</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>9</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>B8/32 G4/43 G4/48</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>ชบา</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I284" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>44.84</v>
+      </c>
+      <c r="M284" t="n">
+        <v>73.27000000000001</v>
+      </c>
+      <c r="N284" t="n">
+        <v>30</v>
+      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>Chevron Offshore / Chaba</t>
+        </is>
+      </c>
+      <c r="S284" t="n">
+        <v>18</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Chevron Offshore</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ในทะเล_G4/48_ยูงทอง</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>9</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>G4/48</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>ยูงทอง</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I285" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M285" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="N285" t="n">
+        <v>30</v>
+      </c>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>Chevron Pattani / Yungthong</t>
+        </is>
+      </c>
+      <c r="S285" t="n">
+        <v>19</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Chevron Pattani</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ในทะเล_14A-16A_อาทิตย์</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>9</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>14A-16A</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>อาทิตย์</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>278.7</v>
+      </c>
+      <c r="I286" t="n">
+        <v>48605.61</v>
+      </c>
+      <c r="J286" t="n">
+        <v>11528.07</v>
+      </c>
+      <c r="K286" t="n">
+        <v>10485.93</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" t="n">
+        <v>59091.54</v>
+      </c>
+      <c r="N286" t="n">
+        <v>30</v>
+      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>PTTEP / Arthit</t>
+        </is>
+      </c>
+      <c r="S286" t="n">
+        <v>20</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>PTTEP</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Malay Basin</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>ในทะเล_G12/48_G12/48</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>9</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>G12/48</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>G12/48</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="I287" t="n">
+        <v>1264.74</v>
+      </c>
+      <c r="J287" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="K287" t="n">
+        <v>118.61</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" t="n">
+        <v>1383.35</v>
+      </c>
+      <c r="N287" t="n">
+        <v>30</v>
+      </c>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>PTTEPI / G12/48</t>
+        </is>
+      </c>
+      <c r="S287" t="n">
+        <v>21</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>ในทะเล_G8/50_G8/50</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>9</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>G8/50</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>G8/50</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>30</v>
+      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>PTTEPI / G8/50</t>
+        </is>
+      </c>
+      <c r="S288" t="n">
+        <v>21</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Malay Basin</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ในทะเล_G1/61_เอราวัณ</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>9</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>เอราวัณ</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>276.97</v>
+      </c>
+      <c r="I289" t="n">
+        <v>48304.37</v>
+      </c>
+      <c r="J289" t="n">
+        <v>8517.940000000001</v>
+      </c>
+      <c r="K289" t="n">
+        <v>7747.92</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" t="n">
+        <v>56052.29</v>
+      </c>
+      <c r="N289" t="n">
+        <v>30</v>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G1/61</t>
+        </is>
+      </c>
+      <c r="S289" t="n">
+        <v>22</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ในทะเล_G1/61_ฟูนาน</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>9</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ฟูนาน</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>146.92</v>
+      </c>
+      <c r="I290" t="n">
+        <v>25623.1</v>
+      </c>
+      <c r="J290" t="n">
+        <v>5007.83</v>
+      </c>
+      <c r="K290" t="n">
+        <v>4555.13</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>30178.23</v>
+      </c>
+      <c r="N290" t="n">
+        <v>30</v>
+      </c>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G1/61</t>
+        </is>
+      </c>
+      <c r="S290" t="n">
+        <v>22</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>ในทะเล_G1/61_ปลาทอง</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>9</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>ปลาทอง</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="I291" t="n">
+        <v>8873.08</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>6993.93</v>
+      </c>
+      <c r="M291" t="n">
+        <v>15867.01</v>
+      </c>
+      <c r="N291" t="n">
+        <v>30</v>
+      </c>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G1/61</t>
+        </is>
+      </c>
+      <c r="S291" t="n">
+        <v>22</v>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ในทะเล_G1/61_ปลาทอง2</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>9</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>ปลาทอง2</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>127.92</v>
+      </c>
+      <c r="I292" t="n">
+        <v>22308.4</v>
+      </c>
+      <c r="J292" t="n">
+        <v>4258.4</v>
+      </c>
+      <c r="K292" t="n">
+        <v>3873.44</v>
+      </c>
+      <c r="L292" t="n">
+        <v>4118.8</v>
+      </c>
+      <c r="M292" t="n">
+        <v>30300.64</v>
+      </c>
+      <c r="N292" t="n">
+        <v>30</v>
+      </c>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G1/61</t>
+        </is>
+      </c>
+      <c r="S292" t="n">
+        <v>22</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>ในทะเล_G1/61_สตูล</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>9</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>G1/61</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>สตูล</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>155.11</v>
+      </c>
+      <c r="I293" t="n">
+        <v>27052</v>
+      </c>
+      <c r="J293" t="n">
+        <v>3194.33</v>
+      </c>
+      <c r="K293" t="n">
+        <v>2905.57</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" t="n">
+        <v>29957.57</v>
+      </c>
+      <c r="N293" t="n">
+        <v>30</v>
+      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G1/61</t>
+        </is>
+      </c>
+      <c r="S293" t="n">
+        <v>22</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>ในทะเล_G2/61_G2N</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>9</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>G2/61</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>G2N</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>393.95</v>
+      </c>
+      <c r="I294" t="n">
+        <v>68706.88</v>
+      </c>
+      <c r="J294" t="n">
+        <v>12096.4</v>
+      </c>
+      <c r="K294" t="n">
+        <v>11002.89</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" t="n">
+        <v>79709.77</v>
+      </c>
+      <c r="N294" t="n">
+        <v>30</v>
+      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G2/61</t>
+        </is>
+      </c>
+      <c r="S294" t="n">
+        <v>23</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>Malay Basin</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>ในทะเล_G2/61_G2S</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>9</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>G2/61</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>G2S</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="I295" t="n">
+        <v>61454.32</v>
+      </c>
+      <c r="J295" t="n">
+        <v>8861.969999999999</v>
+      </c>
+      <c r="K295" t="n">
+        <v>8060.85</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>69515.17</v>
+      </c>
+      <c r="N295" t="n">
+        <v>30</v>
+      </c>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>PTTEP ED / G2/61</t>
+        </is>
+      </c>
+      <c r="S295" t="n">
+        <v>23</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>PTTEP ED</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>Malay Basin</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>PSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>ในทะเล_B8/38_บัวหลวง</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>9</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>B8/38</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>บัวหลวง</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I296" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
+        <v>5879.53</v>
+      </c>
+      <c r="M296" t="n">
+        <v>5884.95</v>
+      </c>
+      <c r="N296" t="n">
+        <v>30</v>
+      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>Medco / Bualuang</t>
+        </is>
+      </c>
+      <c r="S296" t="n">
+        <v>24</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Medco</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Chumphon Basin</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>ในทะเล_G6/48_รสสุคนธ์</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>9</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>G6/48</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>รสสุคนธ์</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="I297" t="n">
+        <v>1315.14</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
+        <v>6440.63</v>
+      </c>
+      <c r="M297" t="n">
+        <v>7755.77</v>
+      </c>
+      <c r="N297" t="n">
+        <v>30</v>
+      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>Northern Gulf Petroleum / Rossukon</t>
+        </is>
+      </c>
+      <c r="S297" t="n">
+        <v>25</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Northern Gulf Petroleum</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ในทะเล_B5/27_จัสมิน บานเย็น</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>9</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>B5/27</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>จัสมิน บานเย็น</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I298" t="n">
+        <v>650.98</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="n">
+        <v>7921.42</v>
+      </c>
+      <c r="M298" t="n">
+        <v>8572.4</v>
+      </c>
+      <c r="N298" t="n">
+        <v>30</v>
+      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>Valeura Energy Jasmine / Jasmine, Banyen</t>
+        </is>
+      </c>
+      <c r="S298" t="n">
+        <v>26</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Valeura Energy Jasmine</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ในทะเล_G1/48_มโนราห์</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>9</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>G1/48</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>มโนราห์</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I299" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
+        <v>2898.16</v>
+      </c>
+      <c r="M299" t="n">
+        <v>2943.45</v>
+      </c>
+      <c r="N299" t="n">
+        <v>30</v>
+      </c>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>Valeura / Manora</t>
+        </is>
+      </c>
+      <c r="S299" t="n">
+        <v>27</v>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Valeura</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>Kra Basin</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>ในทะเล_G11/48_นงเยาว์</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>9</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>G11/48</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>นงเยาว์</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I300" t="n">
+        <v>645.85</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="n">
+        <v>10132.91</v>
+      </c>
+      <c r="M300" t="n">
+        <v>10778.76</v>
+      </c>
+      <c r="N300" t="n">
+        <v>30</v>
+      </c>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>Valeura / Nongyao</t>
+        </is>
+      </c>
+      <c r="S300" t="n">
+        <v>28</v>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Valeura</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>ในทะเล_G10/48_วาสนา</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>9</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>ในทะเล</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>G10/48</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>วาสนา</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I301" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>2387.35</v>
+      </c>
+      <c r="M301" t="n">
+        <v>2389.48</v>
+      </c>
+      <c r="N301" t="n">
+        <v>30</v>
+      </c>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>Offshore</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>Valeura / Wassana</t>
+        </is>
+      </c>
+      <c r="S301" t="n">
+        <v>29</v>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Valeura</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>Pattani Basin</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>บนบก_S1_Sirikit และอื่นๆใน S1</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>9</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Sirikit และอื่นๆใน S1</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="I302" t="n">
+        <v>3497.59</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>25112</v>
+      </c>
+      <c r="M302" t="n">
+        <v>28609.59</v>
+      </c>
+      <c r="N302" t="n">
+        <v>30</v>
+      </c>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>PTTEP Siam / Sirikit and Others</t>
+        </is>
+      </c>
+      <c r="S302" t="n">
+        <v>1</v>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>PTTEP Siam</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>Phitsanulok Basin</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>บนบก_E5_น้ำพอง</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>9</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>น้ำพอง</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="I303" t="n">
+        <v>1421.39</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" t="n">
+        <v>1421.39</v>
+      </c>
+      <c r="N303" t="n">
+        <v>30</v>
+      </c>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R303" t="inlineStr">
+        <is>
+          <t>MH Energy / Nam Phong</t>
+        </is>
+      </c>
+      <c r="S303" t="n">
+        <v>2</v>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>MH Energy</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>Khorat Basin</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>บนบก_EU1_ภูฮ่อม</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>9</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>EU1</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>ภูฮ่อม</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="I304" t="n">
+        <v>16667.48</v>
+      </c>
+      <c r="J304" t="n">
+        <v>193.06</v>
+      </c>
+      <c r="K304" t="n">
+        <v>175.6</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" t="n">
+        <v>16843.08</v>
+      </c>
+      <c r="N304" t="n">
+        <v>30</v>
+      </c>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R304" t="inlineStr">
+        <is>
+          <t>PTTEP SP / Sinphuhorm</t>
+        </is>
+      </c>
+      <c r="S304" t="n">
+        <v>3</v>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>PTTEP SP</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>Khorat Basin</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>บนบก_PTTEP1 L54/43_กำแพงแสน อู่ทอง สังฆจาย หนองผักชี</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>9</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>PTTEP1 L54/43</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>กำแพงแสน อู่ทอง สังฆจาย หนองผักชี</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>734.86</v>
+      </c>
+      <c r="M305" t="n">
+        <v>735.54</v>
+      </c>
+      <c r="N305" t="n">
+        <v>30</v>
+      </c>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R305" t="inlineStr">
+        <is>
+          <t>PTTEPI / Kamphaeng Saen, U Thong, Sangkajai, Nong Phak Chi</t>
+        </is>
+      </c>
+      <c r="S305" t="n">
+        <v>4</v>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>Suphan Buri Basin</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>บนบก_L22/43_วังไผ่สูง</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>9</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>L22/43</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>วังไผ่สูง</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>13</v>
+      </c>
+      <c r="M306" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="N306" t="n">
+        <v>30</v>
+      </c>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>PTTEPI / Wang Phai Sung</t>
+        </is>
+      </c>
+      <c r="S306" t="n">
+        <v>5</v>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>PTTEPI</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>Phitsanulok Basin</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>บนบก_L33/43 L44/43_L33 นาสนุ่นตะวันออก บ่อรังเหนือ</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>9</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>L33/43 L44/43</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L33 นาสนุ่นตะวันออก บ่อรังเหนือ</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I307" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0</v>
+      </c>
+      <c r="L307" t="n">
+        <v>154.33</v>
+      </c>
+      <c r="M307" t="n">
+        <v>164.63</v>
+      </c>
+      <c r="N307" t="n">
+        <v>30</v>
+      </c>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>Eco Orient / L33, East Na Sanun, North Borang</t>
+        </is>
+      </c>
+      <c r="S307" t="n">
+        <v>7</v>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Eco Orient</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>Phetchabun Basin</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>บนบก_L53/48_L53</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>9</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>L53/48</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L53</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I308" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1768.98</v>
+      </c>
+      <c r="M308" t="n">
+        <v>1777.24</v>
+      </c>
+      <c r="N308" t="n">
+        <v>30</v>
+      </c>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R308" t="inlineStr">
+        <is>
+          <t>Pan Orient / L53</t>
+        </is>
+      </c>
+      <c r="S308" t="n">
+        <v>8</v>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>Pan Orient</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>Suphan Buri Basin</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>บนบก_L11/43_บูรพา</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>9</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>L11/43</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>บูรพา</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I309" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L309" t="n">
+        <v>149.04</v>
+      </c>
+      <c r="M309" t="n">
+        <v>160.89</v>
+      </c>
+      <c r="N309" t="n">
+        <v>30</v>
+      </c>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>UAC Utilities / Burapa</t>
+        </is>
+      </c>
+      <c r="S309" t="n">
+        <v>9</v>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>UAC Utilities</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>Phitsanulok Basin</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>บนบก_L10/43_อรุโณทัย</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>9</v>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>L10/43</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>อรุโณทัย</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I310" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="M310" t="n">
+        <v>44.91999999999999</v>
+      </c>
+      <c r="N310" t="n">
+        <v>30</v>
+      </c>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R310" t="inlineStr">
+        <is>
+          <t>UAC Utilities / Arunothai</t>
+        </is>
+      </c>
+      <c r="S310" t="n">
+        <v>10</v>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>UAC Utilities</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>Phitsanulok Basin</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>บนบก_L1/64_L1/64 บึงหญ้า</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>9</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>L1/64</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>L1/64 บึงหญ้า</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I311" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
+        <v>527.01</v>
+      </c>
+      <c r="M311" t="n">
+        <v>562.65</v>
+      </c>
+      <c r="N311" t="n">
+        <v>30</v>
+      </c>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R311" t="inlineStr">
+        <is>
+          <t>CNPCHK / Bung Ya (L1/64)</t>
+        </is>
+      </c>
+      <c r="S311" t="n">
+        <v>11</v>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>CNPCHK</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>Phitsanulok Basin</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Concession</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>บนบก_L21/43_บึงหญ้า ต.ต., หนองสะ บึงม่วง ต.ต.</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>2569</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>กันยายน</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>9</v>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>บนบก</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>L21/43</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>บึงหญ้า ต.ต., หนองสะ บึงม่วง ต.ต.</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I312" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0</v>
+      </c>
+      <c r="L312" t="n">
+        <v>314.2</v>
+      </c>
+      <c r="M312" t="n">
+        <v>334.79</v>
+      </c>
+      <c r="N312" t="n">
+        <v>30</v>
+      </c>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>DMF_createpetroleum_2569_9.xlsx</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Onshore</t>
+        </is>
+      </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>CNPCHK / West Bung Ya &amp; Nong Sa, West Bung Muang</t>
+        </is>
+      </c>
+      <c r="S312" t="n">
+        <v>12</v>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>CNPCHK</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>Phitsanulok Basin</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
         <is>
           <t>Concession</t>
         </is>
